--- a/data/trans_orig/P2A_enfcro_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_enfcro_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2007</t>
+          <t>Hogares según si tienen personas con enfermedades crónicas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>291993</t>
+          <t>291277</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>344265</t>
+          <t>345715</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>385870</t>
+          <t>384938</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>435260</t>
+          <t>436487</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>692446</t>
+          <t>693394</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>764398</t>
+          <t>765634</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,39%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>349747</t>
+          <t>348297</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>402019</t>
+          <t>402735</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>253091</t>
+          <t>251864</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>302481</t>
+          <t>303413</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>617965</t>
+          <t>616729</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>689917</t>
+          <t>688969</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,84%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>406340</t>
+          <t>401856</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>468230</t>
+          <t>465399</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>573297</t>
+          <t>567251</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>632124</t>
+          <t>632703</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>996155</t>
+          <t>992583</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1086634</t>
+          <t>1083421</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,13%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>493570</t>
+          <t>496401</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>555460</t>
+          <t>559944</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>336269</t>
+          <t>335690</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>395096</t>
+          <t>401142</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>843559</t>
+          <t>846772</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>934038</t>
+          <t>937610</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,58%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>277103</t>
+          <t>278236</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>329783</t>
+          <t>330386</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>385848</t>
+          <t>385675</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>437556</t>
+          <t>436721</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>678326</t>
+          <t>679814</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>754186</t>
+          <t>753109</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,28%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>348726</t>
+          <t>348123</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>401406</t>
+          <t>400273</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>246285</t>
+          <t>247120</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>297993</t>
+          <t>298166</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>608164</t>
+          <t>609241</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>684024</t>
+          <t>682536</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,1%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>368121</t>
+          <t>368974</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>428598</t>
+          <t>427055</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>586696</t>
+          <t>581298</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>650672</t>
+          <t>647003</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>968234</t>
+          <t>966457</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1060132</t>
+          <t>1056216</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,32%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>513624</t>
+          <t>515167</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>574101</t>
+          <t>573248</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>387940</t>
+          <t>391609</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>451916</t>
+          <t>457314</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>920702</t>
+          <t>924618</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1012600</t>
+          <t>1014377</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,21%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1395018</t>
+          <t>1395138</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1518207</t>
+          <t>1511228</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1984896</t>
+          <t>1987034</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2100982</t>
+          <t>2098254</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3412677</t>
+          <t>3411780</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3580049</t>
+          <t>3578155</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,76%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1758336</t>
+          <t>1765315</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1881525</t>
+          <t>1881405</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1278215</t>
+          <t>1280943</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1394301</t>
+          <t>1392163</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3075692</t>
+          <t>3077586</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3243064</t>
+          <t>3243961</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,74%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2012</t>
+          <t>Hogares según si tienen personas con enfermedades crónicas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>389620</t>
+          <t>387461</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>441818</t>
+          <t>442132</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>443469</t>
+          <t>444909</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>497373</t>
+          <t>496355</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>851424</t>
+          <t>851502</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>924243</t>
+          <t>926662</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,17%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>261651</t>
+          <t>261337</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>313849</t>
+          <t>316008</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>199677</t>
+          <t>200695</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>253581</t>
+          <t>252141</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>476276</t>
+          <t>473857</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>549095</t>
+          <t>549017</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,2%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>499227</t>
+          <t>498279</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>564943</t>
+          <t>563668</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>681431</t>
+          <t>678813</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>743672</t>
+          <t>741859</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1193231</t>
+          <t>1194307</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1288630</t>
+          <t>1284820</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,67%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>453004</t>
+          <t>454279</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>518720</t>
+          <t>519668</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>288512</t>
+          <t>290325</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>350753</t>
+          <t>353371</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>761501</t>
+          <t>765311</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>856900</t>
+          <t>855824</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,74%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>339934</t>
+          <t>340442</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>397702</t>
+          <t>398741</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>486857</t>
+          <t>488128</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>540365</t>
+          <t>541161</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>844434</t>
+          <t>848785</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>923144</t>
+          <t>927005</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,4%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>359921</t>
+          <t>358882</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>417689</t>
+          <t>417181</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>236809</t>
+          <t>236013</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>290317</t>
+          <t>289046</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>611653</t>
+          <t>607792</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>690363</t>
+          <t>686012</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>44,7%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>499005</t>
+          <t>496530</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>562378</t>
+          <t>559847</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>674902</t>
+          <t>671280</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>736368</t>
+          <t>736171</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1192309</t>
+          <t>1187286</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1276745</t>
+          <t>1277091</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,87%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>385361</t>
+          <t>387892</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>448734</t>
+          <t>451209</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>315533</t>
+          <t>315730</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>376999</t>
+          <t>380621</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>722895</t>
+          <t>722549</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>807331</t>
+          <t>812354</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,63%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1789667</t>
+          <t>1787734</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1908688</t>
+          <t>1905940</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2346785</t>
+          <t>2344188</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2463521</t>
+          <t>2461200</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4170243</t>
+          <t>4171772</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4338258</t>
+          <t>4338291</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1518091</t>
+          <t>1520839</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1637112</t>
+          <t>1639045</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1094788</t>
+          <t>1097109</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1211524</t>
+          <t>1214121</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2646830</t>
+          <t>2646797</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2814845</t>
+          <t>2813316</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,28%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2016</t>
+          <t>Hogares según si tienen personas con enfermedades crónicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>314584</t>
+          <t>315396</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>368477</t>
+          <t>369731</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>391725</t>
+          <t>393087</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>441409</t>
+          <t>444717</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>726308</t>
+          <t>723355</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>797293</t>
+          <t>798079</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,22%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>306323</t>
+          <t>305069</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>360216</t>
+          <t>359404</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>231430</t>
+          <t>228122</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>281114</t>
+          <t>279752</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>550346</t>
+          <t>549560</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>621331</t>
+          <t>624284</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,32%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>463531</t>
+          <t>467785</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>530239</t>
+          <t>532043</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>635362</t>
+          <t>632939</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>696662</t>
+          <t>696624</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1120671</t>
+          <t>1121159</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1213261</t>
+          <t>1211649</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,67%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>492192</t>
+          <t>490388</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>558900</t>
+          <t>554646</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>346251</t>
+          <t>346289</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>407551</t>
+          <t>409974</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>852083</t>
+          <t>853695</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>944673</t>
+          <t>944185</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,72%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>328220</t>
+          <t>327006</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>384663</t>
+          <t>386062</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>427914</t>
+          <t>427886</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>487071</t>
+          <t>485175</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>774614</t>
+          <t>771581</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>854445</t>
+          <t>850539</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,07%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>374889</t>
+          <t>373490</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>431332</t>
+          <t>432546</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>297940</t>
+          <t>299836</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>357097</t>
+          <t>357125</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>690118</t>
+          <t>694024</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>769949</t>
+          <t>772982</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>50,05%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>459711</t>
+          <t>459407</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>519496</t>
+          <t>517461</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>596461</t>
+          <t>596512</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>659670</t>
+          <t>663359</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1077153</t>
+          <t>1074160</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1166599</t>
+          <t>1161134</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,6%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>418071</t>
+          <t>420106</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>477856</t>
+          <t>478160</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>384109</t>
+          <t>380420</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>447318</t>
+          <t>447267</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>814747</t>
+          <t>820212</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>904193</t>
+          <t>907186</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,79%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1628133</t>
+          <t>1629433</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1749665</t>
+          <t>1743343</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2113439</t>
+          <t>2119804</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2230684</t>
+          <t>2232713</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3773554</t>
+          <t>3775991</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3942718</t>
+          <t>3938798</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,76%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1644685</t>
+          <t>1651007</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1766217</t>
+          <t>1764917</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1313858</t>
+          <t>1311829</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1431103</t>
+          <t>1424738</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2996174</t>
+          <t>3000094</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3165338</t>
+          <t>3162901</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,58%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2023</t>
+          <t>Hogares según si tienen personas con enfermedades crónicas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>218837</t>
+          <t>221322</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>273584</t>
+          <t>274297</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>222863</t>
+          <t>229429</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>325222</t>
+          <t>324460</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>474779</t>
+          <t>474758</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>578712</t>
+          <t>579718</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,6%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>361857</t>
+          <t>361144</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>416604</t>
+          <t>414119</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>400108</t>
+          <t>400870</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>502467</t>
+          <t>495901</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>782060</t>
+          <t>781054</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>885993</t>
+          <t>886014</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>186341</t>
+          <t>158613</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>441454</t>
+          <t>439824</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>391244</t>
+          <t>392196</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>444307</t>
+          <t>448576</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>497622</t>
+          <t>503331</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>872290</t>
+          <t>871923</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,53%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>751410</t>
+          <t>753040</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1006523</t>
+          <t>1034251</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>514344</t>
+          <t>510075</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>567407</t>
+          <t>566455</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1279226</t>
+          <t>1279593</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1653894</t>
+          <t>1648185</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,61%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>196693</t>
+          <t>200342</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>256363</t>
+          <t>255804</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>309180</t>
+          <t>304905</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>672558</t>
+          <t>686321</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>531068</t>
+          <t>527521</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1005974</t>
+          <t>987551</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>60,29%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>448317</t>
+          <t>448876</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>507987</t>
+          <t>504338</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>260808</t>
+          <t>247045</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>624186</t>
+          <t>628461</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>632072</t>
+          <t>650495</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1106978</t>
+          <t>1110525</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,8%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>260916</t>
+          <t>264998</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>325084</t>
+          <t>326689</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>322239</t>
+          <t>320853</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>432846</t>
+          <t>436712</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>606924</t>
+          <t>602999</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>735585</t>
+          <t>737660</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,49%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>601747</t>
+          <t>600142</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>665915</t>
+          <t>661833</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>662086</t>
+          <t>658220</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>772693</t>
+          <t>774079</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1286178</t>
+          <t>1284103</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1414839</t>
+          <t>1418764</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,17%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>878030</t>
+          <t>851461</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1217031</t>
+          <t>1212100</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1417449</t>
+          <t>1412102</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1988813</t>
+          <t>1968520</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2415351</t>
+          <t>2428411</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3070970</t>
+          <t>3056824</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,62%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2242786</t>
+          <t>2247717</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2581787</t>
+          <t>2608356</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1723467</t>
+          <t>1743760</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2294831</t>
+          <t>2300178</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4101127</t>
+          <t>4115273</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4756746</t>
+          <t>4743686</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,14%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_enfcro_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_enfcro_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>291277</t>
+          <t>291617</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>345715</t>
+          <t>343784</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>384938</t>
+          <t>386046</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>436487</t>
+          <t>434078</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>693394</t>
+          <t>689937</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>765634</t>
+          <t>763720</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,25%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>348297</t>
+          <t>350228</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>402735</t>
+          <t>402395</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>251864</t>
+          <t>254273</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>303413</t>
+          <t>302305</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>616729</t>
+          <t>618643</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>688969</t>
+          <t>692426</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>50,09%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>401856</t>
+          <t>403482</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>465399</t>
+          <t>468854</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>567251</t>
+          <t>572298</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>632703</t>
+          <t>633951</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>992583</t>
+          <t>996018</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1083421</t>
+          <t>1084979</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,21%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>496401</t>
+          <t>492946</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>559944</t>
+          <t>558318</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>335690</t>
+          <t>334442</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>401142</t>
+          <t>396095</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>846772</t>
+          <t>845214</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>937610</t>
+          <t>934175</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,4%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>278236</t>
+          <t>276565</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>330386</t>
+          <t>332029</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>385675</t>
+          <t>386904</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>436721</t>
+          <t>436362</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>679814</t>
+          <t>677312</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>753109</t>
+          <t>753613</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,32%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>348123</t>
+          <t>346480</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>400273</t>
+          <t>401944</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>247120</t>
+          <t>247479</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>298166</t>
+          <t>296937</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>609241</t>
+          <t>608737</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>682536</t>
+          <t>685038</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>50,28%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>368974</t>
+          <t>366545</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>427055</t>
+          <t>428482</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>581298</t>
+          <t>583005</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>647003</t>
+          <t>649828</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>966457</t>
+          <t>969836</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1056216</t>
+          <t>1056016</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,31%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>515167</t>
+          <t>513740</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>573248</t>
+          <t>575677</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>391609</t>
+          <t>388784</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>457314</t>
+          <t>455607</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>924618</t>
+          <t>924818</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1014377</t>
+          <t>1010998</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,04%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1395138</t>
+          <t>1400719</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1511228</t>
+          <t>1511926</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1987034</t>
+          <t>1983020</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2098254</t>
+          <t>2093417</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3411780</t>
+          <t>3414949</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3578155</t>
+          <t>3578136</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1765315</t>
+          <t>1764617</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1881405</t>
+          <t>1875824</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1280943</t>
+          <t>1285780</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1392163</t>
+          <t>1396177</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3077586</t>
+          <t>3077605</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3243961</t>
+          <t>3240792</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,69%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>387461</t>
+          <t>386390</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>442132</t>
+          <t>441268</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>444909</t>
+          <t>446081</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>496355</t>
+          <t>497351</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>851502</t>
+          <t>854057</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>926662</t>
+          <t>926725</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>261337</t>
+          <t>262201</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>316008</t>
+          <t>317079</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>200695</t>
+          <t>199699</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>252141</t>
+          <t>250969</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>473857</t>
+          <t>473794</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>549017</t>
+          <t>546462</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,02%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>498279</t>
+          <t>499632</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>563668</t>
+          <t>566444</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>678813</t>
+          <t>676691</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>741859</t>
+          <t>741099</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1194307</t>
+          <t>1193837</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1284820</t>
+          <t>1285118</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,68%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>454279</t>
+          <t>451503</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>519668</t>
+          <t>518315</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>290325</t>
+          <t>291085</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>353371</t>
+          <t>355493</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>765311</t>
+          <t>765013</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>855824</t>
+          <t>856294</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,77%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>340442</t>
+          <t>339472</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>398741</t>
+          <t>398963</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>488128</t>
+          <t>486536</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>541161</t>
+          <t>540613</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>848785</t>
+          <t>842687</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>927005</t>
+          <t>925810</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,32%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>358882</t>
+          <t>358660</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>417181</t>
+          <t>418151</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>236013</t>
+          <t>236561</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>289046</t>
+          <t>290638</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>607792</t>
+          <t>608987</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>686012</t>
+          <t>692110</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>45,09%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>496530</t>
+          <t>498359</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>559847</t>
+          <t>560687</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>671280</t>
+          <t>671897</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>736171</t>
+          <t>733506</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1187286</t>
+          <t>1193559</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1277091</t>
+          <t>1278340</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,93%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>387892</t>
+          <t>387052</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>451209</t>
+          <t>449380</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>315730</t>
+          <t>318395</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>380621</t>
+          <t>380004</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>722549</t>
+          <t>721300</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>812354</t>
+          <t>806081</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,31%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1787734</t>
+          <t>1781529</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1905940</t>
+          <t>1911230</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2344188</t>
+          <t>2343467</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2461200</t>
+          <t>2459148</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4171772</t>
+          <t>4164479</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4338291</t>
+          <t>4334381</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,05%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1520839</t>
+          <t>1515549</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1639045</t>
+          <t>1645250</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1097109</t>
+          <t>1099161</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1214121</t>
+          <t>1214842</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2646797</t>
+          <t>2650707</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2813316</t>
+          <t>2820609</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,38%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>315396</t>
+          <t>314857</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>369731</t>
+          <t>367144</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>393087</t>
+          <t>393800</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>444717</t>
+          <t>444546</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>723355</t>
+          <t>720327</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>798079</t>
+          <t>792005</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>58,77%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>305069</t>
+          <t>307656</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>359404</t>
+          <t>359943</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>228122</t>
+          <t>228293</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>279752</t>
+          <t>279039</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>549560</t>
+          <t>555634</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>624284</t>
+          <t>627312</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,55%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>467785</t>
+          <t>469227</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>532043</t>
+          <t>533846</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>632939</t>
+          <t>631068</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>696624</t>
+          <t>694210</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1121159</t>
+          <t>1117018</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1211649</t>
+          <t>1206753</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,43%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>490388</t>
+          <t>488585</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>554646</t>
+          <t>553204</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>346289</t>
+          <t>348703</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>409974</t>
+          <t>411845</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>853695</t>
+          <t>858591</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>944185</t>
+          <t>948326</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,92%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>327006</t>
+          <t>324309</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>386062</t>
+          <t>386525</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>427886</t>
+          <t>428375</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>485175</t>
+          <t>486476</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>771581</t>
+          <t>769716</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>850539</t>
+          <t>851599</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>55,14%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>373490</t>
+          <t>373027</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>432546</t>
+          <t>435243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>299836</t>
+          <t>298535</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>357125</t>
+          <t>356636</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>694024</t>
+          <t>692964</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>772982</t>
+          <t>774847</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>50,17%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>459407</t>
+          <t>461182</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>517461</t>
+          <t>520045</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>596512</t>
+          <t>599147</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>663359</t>
+          <t>665567</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1074160</t>
+          <t>1070297</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1161134</t>
+          <t>1162090</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,65%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>420106</t>
+          <t>417522</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>478160</t>
+          <t>476385</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>380420</t>
+          <t>378212</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>447267</t>
+          <t>444632</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>820212</t>
+          <t>819256</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>907186</t>
+          <t>911049</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,98%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1629433</t>
+          <t>1624172</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1743343</t>
+          <t>1744035</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2119804</t>
+          <t>2111362</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2232713</t>
+          <t>2229526</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3775991</t>
+          <t>3777097</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3938798</t>
+          <t>3939736</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,78%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1651007</t>
+          <t>1650315</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1764917</t>
+          <t>1770178</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1311829</t>
+          <t>1315016</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1424738</t>
+          <t>1433180</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3000094</t>
+          <t>2999156</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3162901</t>
+          <t>3161795</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>245955</t>
+          <t>258935</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>221322</t>
+          <t>234587</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>274297</t>
+          <t>286334</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>294869</t>
+          <t>322543</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>229429</t>
+          <t>299220</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>324460</t>
+          <t>344324</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>540824</t>
+          <t>581477</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>474758</t>
+          <t>548158</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>579718</t>
+          <t>616930</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>43,3%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>389486</t>
+          <t>431775</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>361144</t>
+          <t>404376</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>414119</t>
+          <t>456123</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>430461</t>
+          <t>411637</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>400870</t>
+          <t>389856</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>495901</t>
+          <t>434960</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>819948</t>
+          <t>843412</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>781054</t>
+          <t>807959</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>886014</t>
+          <t>876731</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>61,53%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>340314</t>
+          <t>363682</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>158613</t>
+          <t>331678</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>439824</t>
+          <t>399555</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>419659</t>
+          <t>463475</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>392196</t>
+          <t>436776</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>448576</t>
+          <t>490668</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>759973</t>
+          <t>827157</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>503331</t>
+          <t>783718</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>871923</t>
+          <t>869733</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>41,02%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>852550</t>
+          <t>685235</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>753040</t>
+          <t>649362</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1034251</t>
+          <t>717239</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>538992</t>
+          <t>607999</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>510075</t>
+          <t>580806</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>566455</t>
+          <t>634698</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1391543</t>
+          <t>1293234</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1279593</t>
+          <t>1250658</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1648185</t>
+          <t>1336673</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>63,04%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>225601</t>
+          <t>244739</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>200342</t>
+          <t>216931</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>255804</t>
+          <t>277649</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>454826</t>
+          <t>277957</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>304905</t>
+          <t>251935</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>686321</t>
+          <t>300861</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>680426</t>
+          <t>522696</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>527521</t>
+          <t>487502</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>987551</t>
+          <t>567426</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>35,13%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>479079</t>
+          <t>558334</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>448876</t>
+          <t>525424</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>504338</t>
+          <t>586142</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>478540</t>
+          <t>534302</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>247045</t>
+          <t>511398</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>628461</t>
+          <t>560324</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>957620</t>
+          <t>1092636</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>650495</t>
+          <t>1047906</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1110525</t>
+          <t>1127830</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>69,82%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>292832</t>
+          <t>294644</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>264998</t>
+          <t>266732</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>326689</t>
+          <t>327584</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>395440</t>
+          <t>419550</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>320853</t>
+          <t>391631</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>436712</t>
+          <t>446915</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>688271</t>
+          <t>714194</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>602999</t>
+          <t>675105</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>737660</t>
+          <t>753665</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>35,73%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>633999</t>
+          <t>695418</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>600142</t>
+          <t>662478</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>661833</t>
+          <t>723330</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>699492</t>
+          <t>699491</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>658220</t>
+          <t>672126</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>774079</t>
+          <t>727410</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1333492</t>
+          <t>1394910</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1284103</t>
+          <t>1355439</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1418764</t>
+          <t>1433999</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>67,99%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1104702</t>
+          <t>1162000</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>851461</t>
+          <t>1106345</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1212100</t>
+          <t>1221352</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1564793</t>
+          <t>1483525</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1412102</t>
+          <t>1433536</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1968520</t>
+          <t>1533086</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2669494</t>
+          <t>2645524</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2428411</t>
+          <t>2567115</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3056824</t>
+          <t>2736520</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>37,64%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2355115</t>
+          <t>2370762</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2247717</t>
+          <t>2311410</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2608356</t>
+          <t>2426417</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2147487</t>
+          <t>2253429</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1743760</t>
+          <t>2203868</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2300178</t>
+          <t>2303418</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4502603</t>
+          <t>4624192</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4115273</t>
+          <t>4533196</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4743686</t>
+          <t>4702601</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>64,69%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_enfcro_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_enfcro_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con enfermedades crónicas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con enfermedades crónicas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con enfermedades crónicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con enfermedades crónicas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
